--- a/UnityTableTool/Data/技能表.xlsx
+++ b/UnityTableTool/Data/技能表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game\UnityTools\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/UnityTableTool/Data/技能表.xlsx
+++ b/UnityTableTool/Data/技能表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game\UnityTools\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Skill_1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="51">
   <si>
     <t>table: Skill</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>## 这是一行不打表的数据</t>
+  </si>
+  <si>
+    <t>asd</t>
   </si>
   <si>
     <t>#test_debug</t>
@@ -1291,10 +1294,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1557,6 +1560,206 @@
       </c>
       <c r="I9" s="2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="2">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="2">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="2">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="2">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="2">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="2">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="2">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="2">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="2">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="2">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="2">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="2">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="2">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="2">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="2">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="2">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="2">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="2">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="2">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="2">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="2">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="2">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="2">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="2">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="2">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="2">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="2">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="2">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="2">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="2">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="2">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="2">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="2">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="2">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="2">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1571,7 +1774,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1688,7 +1891,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">

--- a/UnityTableTool/Data/技能表.xlsx
+++ b/UnityTableTool/Data/技能表.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Skill_1" sheetId="1" r:id="rId1"/>
     <sheet name="Skill_2" sheetId="2" r:id="rId2"/>
+    <sheet name="超级无敌雷霆长表格名字" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="51">
   <si>
     <t>table: Skill</t>
   </si>
@@ -1297,7 +1298,7 @@
   <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1774,7 +1775,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2043,4 +2044,281 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C9" s="2">
+        <v>123123</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/UnityTableTool/Data/技能表.xlsx
+++ b/UnityTableTool/Data/技能表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Skill_1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="51">
   <si>
     <t>table: Skill</t>
   </si>
@@ -1298,7 +1298,7 @@
   <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1564,11 +1564,17 @@
       </c>
     </row>
     <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B10" s="2">
         <v>1004</v>
       </c>
     </row>
     <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="B11" s="2">
         <v>1005</v>
       </c>
@@ -1775,7 +1781,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2052,7 +2058,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/UnityTableTool/Data/技能表.xlsx
+++ b/UnityTableTool/Data/技能表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Skill_1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="50">
   <si>
     <t>table: Skill</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>## 这是一行不打表的数据</t>
-  </si>
-  <si>
-    <t>asd</t>
   </si>
   <si>
     <t>#test_debug</t>
@@ -1295,10 +1292,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1762,11 +1759,6 @@
     <row r="48" spans="2:2">
       <c r="B48" s="2">
         <v>1042</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1773,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1898,7 +1890,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
@@ -2058,7 +2050,7 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="9" width="20.625" style="1" customWidth="1"/>
+    <col min="1" max="9" width="20.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2175,7 +2167,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="15" customHeight="1" spans="1:9">
